--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/sep-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/sep-2026.xlsx
@@ -6515,7 +6515,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -10721,7 +10721,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -14374,7 +14374,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -14569,7 +14569,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -24158,7 +24158,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
@@ -42480,7 +42480,7 @@
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F656" t="inlineStr">
@@ -44349,7 +44349,7 @@
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F685" t="inlineStr">
@@ -44918,7 +44918,7 @@
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F694" t="inlineStr">
@@ -49095,7 +49095,7 @@
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F759" t="inlineStr">
@@ -51545,7 +51545,7 @@
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F797" t="inlineStr">
@@ -54312,7 +54312,7 @@
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F840" t="inlineStr">
@@ -54832,7 +54832,7 @@
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F848" t="inlineStr">
@@ -55917,7 +55917,7 @@
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F865" t="inlineStr">
@@ -56429,7 +56429,7 @@
       </c>
       <c r="E873" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F873" t="inlineStr">
@@ -56616,7 +56616,7 @@
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F876" t="inlineStr">
@@ -57388,7 +57388,7 @@
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F888" t="inlineStr">
@@ -58928,7 +58928,7 @@
       </c>
       <c r="E912" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F912" t="inlineStr">
@@ -59314,7 +59314,7 @@
       </c>
       <c r="E918" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F918" t="inlineStr">
